--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:16:54+00:00</t>
+    <t>2026-08-26T12:41:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:41:44+00:00</t>
+    <t>2026-08-26T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:53:00+00:00</t>
+    <t>2026-08-26T12:57:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:57:55+00:00</t>
+    <t>2026-08-26T13:02:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:02:54+00:00</t>
+    <t>2026-08-26T13:06:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:06:53+00:00</t>
+    <t>2026-08-26T13:20:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:20:27+00:00</t>
+    <t>2026-08-26T13:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:28:09+00:00</t>
+    <t>2026-08-26T13:31:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:31:50+00:00</t>
+    <t>2026-08-27T12:43:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:43:51+00:00</t>
+    <t>2026-08-28T07:28:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:28:24+00:00</t>
+    <t>2026-08-28T07:52:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:52:50+00:00</t>
+    <t>2026-08-28T08:32:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:32:44+00:00</t>
+    <t>2026-08-28T09:25:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:46:48+00:00</t>
+    <t>2026-08-31T16:02:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T16:02:27+00:00</t>
+    <t>2026-08-31T20:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:20:10+00:00</t>
+    <t>2026-08-31T20:24:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:24:53+00:00</t>
+    <t>2026-09-01T08:07:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:07:41+00:00</t>
+    <t>2026-09-01T08:58:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:58:43+00:00</t>
+    <t>2026-09-01T09:49:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:49:43+00:00</t>
+    <t>2026-09-01T09:54:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:54:08+00:00</t>
+    <t>2026-09-01T09:59:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:59:02+00:00</t>
+    <t>2026-09-01T13:10:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:10:54+00:00</t>
+    <t>2026-09-01T13:41:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:41:09+00:00</t>
+    <t>2026-09-03T13:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T13:48:05+00:00</t>
+    <t>2026-09-03T16:09:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T16:09:48+00:00</t>
+    <t>2026-09-04T09:46:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:46:57+00:00</t>
+    <t>2026-09-04T09:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:58:25+00:00</t>
+    <t>2026-09-08T12:47:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
